--- a/programacao-enpemt2026.xlsx
+++ b/programacao-enpemt2026.xlsx
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Cafezinho com Palco Aberto</t>
+          <t>Coffee Break com Palco Aberto</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr"/>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>Cafezinho</t>
+          <t>Coffeebreak</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr"/>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Cafezinho com Palco Aberto</t>
+          <t>Coffee Break com Palco Aberto</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr"/>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>Cafezinho</t>
+          <t>Coffeebreak</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr"/>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Cafezinho com Palco Aberto</t>
+          <t>Coffee Break com Palco Aberto</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr"/>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>Cafezinho</t>
+          <t>Coffeebreak</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr"/>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Cafezinho com Palco Aberto</t>
+          <t>Coffee Break com Palco Aberto</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr"/>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>Cafezinho</t>
+          <t>Coffeebreak</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr"/>
